--- a/Другое/2026/Доходы.xlsx
+++ b/Другое/2026/Доходы.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="13">
   <si>
     <t>Дата</t>
   </si>
@@ -1095,9 +1095,15 @@
       <c r="C28" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D28" s="12"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="14"/>
+      <c r="D28" s="12">
+        <v>46283</v>
+      </c>
+      <c r="E28" s="13">
+        <v>38575.449999999997</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="29" spans="1:10" ht="15.75" thickBot="1">
       <c r="A29" s="3">
@@ -1109,8 +1115,12 @@
       <c r="C29" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D29" s="12"/>
-      <c r="E29" s="13"/>
+      <c r="D29" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="13">
+        <v>0</v>
+      </c>
       <c r="F29" s="14"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" thickBot="1">
@@ -1358,7 +1368,7 @@
       </c>
       <c r="E46" s="7">
         <f>SUM(E3:E45)</f>
-        <v>990774.32000000007</v>
+        <v>1029349.77</v>
       </c>
       <c r="F46" s="8"/>
     </row>
@@ -1376,7 +1386,7 @@
       </c>
       <c r="E47" s="7">
         <f>E46/8</f>
-        <v>123846.79000000001</v>
+        <v>128668.72125</v>
       </c>
       <c r="F47" s="7"/>
     </row>
@@ -1412,7 +1422,7 @@
       </c>
       <c r="E49" s="10">
         <f>E48/E46</f>
-        <v>0.25008924333040844</v>
+        <v>0.24071701108943755</v>
       </c>
       <c r="F49" s="8"/>
     </row>

--- a/Другое/2026/Доходы.xlsx
+++ b/Другое/2026/Доходы.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="13">
   <si>
     <t>Дата</t>
   </si>
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -246,6 +246,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -542,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" style="1" customWidth="1"/>
@@ -1124,29 +1130,36 @@
       <c r="F29" s="14"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A30" s="3">
-        <v>46298</v>
+      <c r="A30" s="26" t="s">
+        <v>12</v>
       </c>
       <c r="B30" s="4">
-        <f>83130-B26</f>
-        <v>50229</v>
+        <v>0</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30" s="12"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="14"/>
+        <v>12</v>
+      </c>
+      <c r="D30" s="25">
+        <v>46287</v>
+      </c>
+      <c r="E30" s="13">
+        <f>42933+70637+21986</f>
+        <v>135556</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="31" spans="1:10" ht="15.75" thickBot="1">
       <c r="A31" s="3">
         <v>46298</v>
       </c>
       <c r="B31" s="4">
-        <v>32901</v>
+        <f>83130-B26</f>
+        <v>50229</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D31" s="12"/>
       <c r="E31" s="13"/>
@@ -1154,14 +1167,13 @@
     </row>
     <row r="32" spans="1:10" ht="15.75" thickBot="1">
       <c r="A32" s="3">
-        <v>46315</v>
+        <v>46298</v>
       </c>
       <c r="B32" s="4">
-        <f>65476-B33</f>
-        <v>32575</v>
+        <v>32901</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="13"/>
@@ -1172,10 +1184,11 @@
         <v>46315</v>
       </c>
       <c r="B33" s="4">
-        <v>32901</v>
+        <f>65476-B34</f>
+        <v>32575</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D33" s="12"/>
       <c r="E33" s="13"/>
@@ -1183,7 +1196,7 @@
     </row>
     <row r="34" spans="1:6" ht="15.75" thickBot="1">
       <c r="A34" s="3">
-        <v>46324</v>
+        <v>46315</v>
       </c>
       <c r="B34" s="4">
         <v>32901</v>
@@ -1197,14 +1210,13 @@
     </row>
     <row r="35" spans="1:6" ht="15.75" thickBot="1">
       <c r="A35" s="3">
-        <v>46331</v>
+        <v>46324</v>
       </c>
       <c r="B35" s="4">
-        <f>65942-(B34/2)</f>
-        <v>49491.5</v>
+        <v>32901</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35" s="12"/>
       <c r="E35" s="13"/>
@@ -1215,11 +1227,11 @@
         <v>46331</v>
       </c>
       <c r="B36" s="4">
-        <f>62942-B35</f>
-        <v>13450.5</v>
+        <f>65942-(B35/2)</f>
+        <v>49491.5</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="13"/>
@@ -1227,13 +1239,14 @@
     </row>
     <row r="37" spans="1:6" ht="15.75" thickBot="1">
       <c r="A37" s="3">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="B37" s="4">
-        <v>16406</v>
+        <f>62942-B36</f>
+        <v>13450.5</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="13"/>
@@ -1241,13 +1254,13 @@
     </row>
     <row r="38" spans="1:6" ht="15.75" thickBot="1">
       <c r="A38" s="3">
-        <v>46346</v>
+        <v>46332</v>
       </c>
       <c r="B38" s="4">
-        <v>27274</v>
+        <v>16406</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="13"/>
@@ -1258,10 +1271,10 @@
         <v>46346</v>
       </c>
       <c r="B39" s="4">
-        <v>32902</v>
+        <v>27274</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="13"/>
@@ -1269,11 +1282,10 @@
     </row>
     <row r="40" spans="1:6" ht="15.75" thickBot="1">
       <c r="A40" s="3">
-        <v>46361</v>
+        <v>46346</v>
       </c>
       <c r="B40" s="4">
-        <f>79656-47500</f>
-        <v>32156</v>
+        <v>32902</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>5</v>
@@ -1287,11 +1299,11 @@
         <v>46361</v>
       </c>
       <c r="B41" s="4">
-        <f>79656-B40</f>
-        <v>47500</v>
+        <f>79656-47500</f>
+        <v>32156</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D41" s="12"/>
       <c r="E41" s="13"/>
@@ -1299,13 +1311,14 @@
     </row>
     <row r="42" spans="1:6" ht="15.75" thickBot="1">
       <c r="A42" s="3">
-        <v>46375</v>
+        <v>46361</v>
       </c>
       <c r="B42" s="4">
-        <v>32902</v>
+        <f>79656-B41</f>
+        <v>47500</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="13"/>
@@ -1316,10 +1329,10 @@
         <v>46375</v>
       </c>
       <c r="B43" s="4">
-        <v>28788</v>
+        <v>32902</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D43" s="12"/>
       <c r="E43" s="13"/>
@@ -1327,13 +1340,13 @@
     </row>
     <row r="44" spans="1:6" ht="15.75" thickBot="1">
       <c r="A44" s="3">
-        <v>46381</v>
+        <v>46375</v>
       </c>
       <c r="B44" s="4">
-        <v>47500</v>
+        <v>28788</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="13"/>
@@ -1344,87 +1357,101 @@
         <v>46381</v>
       </c>
       <c r="B45" s="4">
-        <f>201149-B44</f>
-        <v>153649</v>
+        <v>47500</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="13"/>
       <c r="F45" s="14"/>
     </row>
     <row r="46" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A46" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B46" s="7">
-        <f>SUM(B3:B45)</f>
-        <v>1585385.3900000001</v>
-      </c>
-      <c r="C46" s="8"/>
-      <c r="D46" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E46" s="7">
-        <f>SUM(E3:E45)</f>
-        <v>1029349.77</v>
-      </c>
-      <c r="F46" s="8"/>
+      <c r="A46" s="3">
+        <v>46381</v>
+      </c>
+      <c r="B46" s="4">
+        <f>201149-B45</f>
+        <v>153649</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46" s="12"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="14"/>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
       <c r="A47" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B47" s="7">
-        <f>B46/12</f>
-        <v>132115.44916666669</v>
-      </c>
-      <c r="C47" s="7"/>
+        <f>SUM(B3:B46)</f>
+        <v>1585385.3900000001</v>
+      </c>
+      <c r="C47" s="8"/>
       <c r="D47" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E47" s="7">
-        <f>E46/8</f>
-        <v>128668.72125</v>
+        <f>SUM(E3:E46)</f>
+        <v>1164905.77</v>
       </c>
       <c r="F47" s="7"/>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
       <c r="A48" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="7">
+        <f>B47/12</f>
+        <v>132115.44916666669</v>
+      </c>
+      <c r="C48" s="7"/>
+      <c r="D48" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="7">
+        <f>E47/8</f>
+        <v>145613.22125</v>
+      </c>
+      <c r="F48" s="7"/>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A49" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B48" s="7">
-        <f>SUMIF(C3:C45, "Премия", B3:B45)</f>
+      <c r="B49" s="7">
+        <f>SUMIF(C3:C46, "Премия", B3:B46)</f>
         <v>538222.5</v>
       </c>
-      <c r="C48" s="8"/>
-      <c r="D48" s="6" t="s">
+      <c r="C49" s="8"/>
+      <c r="D49" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E48" s="7">
-        <f>SUMIF(F3:F45, "Премия", E3:E45)</f>
+      <c r="E49" s="7">
+        <f>SUMIF(F3:F46, "Премия", E3:E46)</f>
         <v>247782</v>
       </c>
-      <c r="F48" s="8"/>
-    </row>
-    <row r="49" spans="1:6" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A49" s="9" t="s">
+      <c r="F49" s="8"/>
+    </row>
+    <row r="50" spans="1:6" ht="35.25" customHeight="1" thickBot="1">
+      <c r="A50" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B49" s="10">
-        <f>B48/B46</f>
+      <c r="B50" s="10">
+        <f>B49/B47</f>
         <v>0.3394900087984285</v>
       </c>
-      <c r="C49" s="8"/>
-      <c r="D49" s="9" t="s">
+      <c r="C50" s="8"/>
+      <c r="D50" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E49" s="10">
-        <f>E48/E46</f>
-        <v>0.24071701108943755</v>
-      </c>
-      <c r="F49" s="8"/>
+      <c r="E50" s="10">
+        <f>E49/E47</f>
+        <v>0.21270561652381548</v>
+      </c>
+      <c r="F50" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Другое/2026/Доходы.xlsx
+++ b/Другое/2026/Доходы.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="13">
   <si>
     <t>Дата</t>
   </si>
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -230,6 +230,12 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -249,10 +255,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -548,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" style="1" customWidth="1"/>
@@ -585,16 +591,16 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="33" thickBot="1">
-      <c r="A2" s="19">
+      <c r="A2" s="21">
         <v>2025</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="22">
+      <c r="B2" s="22"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="24">
         <v>2026</v>
       </c>
-      <c r="E2" s="23"/>
-      <c r="F2" s="24"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="26"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" thickBot="1">
       <c r="A3" s="3">
@@ -806,8 +812,12 @@
       <c r="C13" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="13"/>
+      <c r="D13" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="13">
+        <v>0</v>
+      </c>
       <c r="F13" s="14"/>
     </row>
     <row r="14" spans="1:6" ht="15.75" thickBot="1">
@@ -872,8 +882,12 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A17" s="3"/>
-      <c r="B17" s="4"/>
+      <c r="A17" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="4">
+        <v>0</v>
+      </c>
       <c r="C17" s="5"/>
       <c r="D17" s="12">
         <v>46196</v>
@@ -1130,7 +1144,7 @@
       <c r="F29" s="14"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A30" s="26" t="s">
+      <c r="A30" s="20" t="s">
         <v>12</v>
       </c>
       <c r="B30" s="4">
@@ -1139,7 +1153,7 @@
       <c r="C30" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D30" s="25">
+      <c r="D30" s="19">
         <v>46287</v>
       </c>
       <c r="E30" s="13">
@@ -1161,9 +1175,13 @@
       <c r="C31" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D31" s="12"/>
+      <c r="D31" s="12">
+        <v>46300</v>
+      </c>
       <c r="E31" s="13"/>
-      <c r="F31" s="14"/>
+      <c r="F31" s="14" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="32" spans="1:10" ht="15.75" thickBot="1">
       <c r="A32" s="3">
@@ -1175,34 +1193,42 @@
       <c r="C32" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D32" s="12"/>
+      <c r="D32" s="12">
+        <v>46300</v>
+      </c>
       <c r="E32" s="13"/>
-      <c r="F32" s="14"/>
+      <c r="F32" s="14" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A33" s="3">
-        <v>46315</v>
+      <c r="A33" s="28" t="s">
+        <v>12</v>
       </c>
       <c r="B33" s="4">
-        <f>65476-B34</f>
-        <v>32575</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="12"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="14"/>
+        <v>0</v>
+      </c>
+      <c r="C33" s="5"/>
+      <c r="D33" s="12">
+        <v>46307</v>
+      </c>
+      <c r="E33" s="13">
+        <v>55867</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" thickBot="1">
       <c r="A34" s="3">
         <v>46315</v>
       </c>
       <c r="B34" s="4">
-        <v>32901</v>
+        <f>65476-B35</f>
+        <v>32575</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="13"/>
@@ -1210,7 +1236,7 @@
     </row>
     <row r="35" spans="1:6" ht="15.75" thickBot="1">
       <c r="A35" s="3">
-        <v>46324</v>
+        <v>46315</v>
       </c>
       <c r="B35" s="4">
         <v>32901</v>
@@ -1224,14 +1250,13 @@
     </row>
     <row r="36" spans="1:6" ht="15.75" thickBot="1">
       <c r="A36" s="3">
-        <v>46331</v>
+        <v>46324</v>
       </c>
       <c r="B36" s="4">
-        <f>65942-(B35/2)</f>
-        <v>49491.5</v>
+        <v>32901</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="13"/>
@@ -1242,11 +1267,11 @@
         <v>46331</v>
       </c>
       <c r="B37" s="4">
-        <f>62942-B36</f>
-        <v>13450.5</v>
+        <f>65942-(B36/2)</f>
+        <v>49491.5</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="13"/>
@@ -1254,13 +1279,14 @@
     </row>
     <row r="38" spans="1:6" ht="15.75" thickBot="1">
       <c r="A38" s="3">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="B38" s="4">
-        <v>16406</v>
+        <f>62942-B37</f>
+        <v>13450.5</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="13"/>
@@ -1268,13 +1294,13 @@
     </row>
     <row r="39" spans="1:6" ht="15.75" thickBot="1">
       <c r="A39" s="3">
-        <v>46346</v>
+        <v>46332</v>
       </c>
       <c r="B39" s="4">
-        <v>27274</v>
+        <v>16406</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="13"/>
@@ -1285,10 +1311,10 @@
         <v>46346</v>
       </c>
       <c r="B40" s="4">
-        <v>32902</v>
+        <v>27274</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="13"/>
@@ -1296,11 +1322,10 @@
     </row>
     <row r="41" spans="1:6" ht="15.75" thickBot="1">
       <c r="A41" s="3">
-        <v>46361</v>
+        <v>46346</v>
       </c>
       <c r="B41" s="4">
-        <f>79656-47500</f>
-        <v>32156</v>
+        <v>32902</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>5</v>
@@ -1314,11 +1339,11 @@
         <v>46361</v>
       </c>
       <c r="B42" s="4">
-        <f>79656-B41</f>
-        <v>47500</v>
+        <f>79656-47500</f>
+        <v>32156</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="13"/>
@@ -1326,13 +1351,14 @@
     </row>
     <row r="43" spans="1:6" ht="15.75" thickBot="1">
       <c r="A43" s="3">
-        <v>46375</v>
+        <v>46361</v>
       </c>
       <c r="B43" s="4">
-        <v>32902</v>
+        <f>79656-B42</f>
+        <v>47500</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D43" s="12"/>
       <c r="E43" s="13"/>
@@ -1343,10 +1369,10 @@
         <v>46375</v>
       </c>
       <c r="B44" s="4">
-        <v>28788</v>
+        <v>32902</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="13"/>
@@ -1354,13 +1380,13 @@
     </row>
     <row r="45" spans="1:6" ht="15.75" thickBot="1">
       <c r="A45" s="3">
-        <v>46381</v>
+        <v>46375</v>
       </c>
       <c r="B45" s="4">
-        <v>47500</v>
+        <v>28788</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="13"/>
@@ -1371,87 +1397,101 @@
         <v>46381</v>
       </c>
       <c r="B46" s="4">
-        <f>201149-B45</f>
-        <v>153649</v>
+        <v>47500</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="13"/>
       <c r="F46" s="14"/>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B47" s="7">
-        <f>SUM(B3:B46)</f>
-        <v>1585385.3900000001</v>
-      </c>
-      <c r="C47" s="8"/>
-      <c r="D47" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E47" s="7">
-        <f>SUM(E3:E46)</f>
-        <v>1164905.77</v>
-      </c>
-      <c r="F47" s="7"/>
+      <c r="A47" s="3">
+        <v>46381</v>
+      </c>
+      <c r="B47" s="4">
+        <f>201149-B46</f>
+        <v>153649</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47" s="12"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="14"/>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
       <c r="A48" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B48" s="7">
-        <f>B47/12</f>
-        <v>132115.44916666669</v>
-      </c>
-      <c r="C48" s="7"/>
+        <f>SUM(B3:B47)</f>
+        <v>1585385.3900000001</v>
+      </c>
+      <c r="C48" s="8"/>
       <c r="D48" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E48" s="7">
-        <f>E47/8</f>
-        <v>145613.22125</v>
+        <f>SUM(E3:E47)</f>
+        <v>1220772.77</v>
       </c>
       <c r="F48" s="7"/>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
       <c r="A49" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="7">
+        <f>B48/12</f>
+        <v>132115.44916666669</v>
+      </c>
+      <c r="C49" s="7"/>
+      <c r="D49" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="7">
+        <f>E48/9</f>
+        <v>135641.4188888889</v>
+      </c>
+      <c r="F49" s="7"/>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A50" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B49" s="7">
-        <f>SUMIF(C3:C46, "Премия", B3:B46)</f>
+      <c r="B50" s="7">
+        <f>SUMIF(C3:C47, "Премия", B3:B47)</f>
         <v>538222.5</v>
       </c>
-      <c r="C49" s="8"/>
-      <c r="D49" s="6" t="s">
+      <c r="C50" s="8"/>
+      <c r="D50" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E49" s="7">
-        <f>SUMIF(F3:F46, "Премия", E3:E46)</f>
-        <v>247782</v>
-      </c>
-      <c r="F49" s="8"/>
-    </row>
-    <row r="50" spans="1:6" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A50" s="9" t="s">
+      <c r="E50" s="7">
+        <f>SUMIF(F3:F47, "Премия", E3:E47)</f>
+        <v>303649</v>
+      </c>
+      <c r="F50" s="8"/>
+    </row>
+    <row r="51" spans="1:6" ht="35.25" customHeight="1" thickBot="1">
+      <c r="A51" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B50" s="10">
-        <f>B49/B47</f>
+      <c r="B51" s="10">
+        <f>B50/B48</f>
         <v>0.3394900087984285</v>
       </c>
-      <c r="C50" s="8"/>
-      <c r="D50" s="9" t="s">
+      <c r="C51" s="8"/>
+      <c r="D51" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E50" s="10">
-        <f>E49/E47</f>
-        <v>0.21270561652381548</v>
-      </c>
-      <c r="F50" s="8"/>
+      <c r="E51" s="10">
+        <f>E50/E48</f>
+        <v>0.24873506967230272</v>
+      </c>
+      <c r="F51" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
